--- a/Convites/guest_links.xlsx
+++ b/Convites/guest_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2 de Agosto de 2026</t>
+          <t>15 de Agosto de 2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2 de Agosto de 2026</t>
+          <t>August 15, 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2 de Agosto de 2026</t>
+          <t>15 de Agosto de 2026/August 15, 2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2 de Agosto de 2026</t>
+          <t>15 de Agosto de 2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2 de Agosto de 2026</t>
+          <t>15 de Agosto de 2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2 de Agosto de 2026</t>
+          <t>15 de Agosto de 2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -550,17 +550,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Beatriz, Ricardo, Helena</t>
+          <t>Beatriz, Ricardo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2 de Agosto de 2026</t>
+          <t>15 de Agosto de 2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://casamento-hl.github.io/HeloLuis/Convites/BeatrizRicardoHelena.html</t>
+          <t>https://casamento-hl.github.io/HeloLuis/Convites/BeatrizRicardo.html</t>
         </is>
       </c>
     </row>
@@ -572,12 +572,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2 de Agosto de 2026</t>
+          <t>August 15, 2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>https://casamento-hl.github.io/HeloLuis/Convites/Silke.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BIF</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>August 15, 2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://casamento-hl.github.io/HeloLuis/Convites/BIF.html</t>
         </is>
       </c>
     </row>

--- a/Convites/guest_links.xlsx
+++ b/Convites/guest_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,6 +598,40 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Silvia,José</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15 de Agosto de 2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://casamento-hl.github.io/HeloLuis/Convites/Silvia,José.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Marina, Jhon</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15 de Agosto de 2026/August 15, 2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://casamento-hl.github.io/HeloLuis/Convites/MarinaJhon.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Convites/guest_links.xlsx
+++ b/Convites/guest_links.xlsx
@@ -601,7 +601,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Silvia,José</t>
+          <t>Silvia, José</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://casamento-hl.github.io/HeloLuis/Convites/Silvia,José.html</t>
+          <t>https://casamento-hl.github.io/HeloLuis/Convites/SilviaJosé.html</t>
         </is>
       </c>
     </row>
